--- a/excel_files/其他科目.xlsx
+++ b/excel_files/其他科目.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\dist\執行_工作日誌填寫系統_App20260616\excel_files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B7185AE-4944-4677-9EEF-E726C3CD5B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1086E7BC-D799-40C7-B166-F5715C557F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5854D81B-5B7B-4871-9FA3-56C4511C9373}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
   <si>
     <t>工程案號</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -43,18 +43,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>工安</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>教育訓練</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>採購</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>財務</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -83,15 +75,15 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>工務部</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>設計業務部</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t xml:space="preserve"> </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -586,7 +578,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -594,103 +586,99 @@
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="2" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15" spans="1:2">
-      <c r="A15" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="A15" s="2"/>
       <c r="B15" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2">
-      <c r="A16" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="A16" s="2"/>
       <c r="B16" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="17" spans="1:2">

--- a/excel_files/其他科目.xlsx
+++ b/excel_files/其他科目.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1086E7BC-D799-40C7-B166-F5715C557F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F8696-E18A-497D-8623-E8B40B37BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5854D81B-5B7B-4871-9FA3-56C4511C9373}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>工程案號</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -35,56 +35,35 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>修繕</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>環境</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>教育訓練</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>財務</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>會計</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>行政</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>人事</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>車輛</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>研發</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>MIS</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>設計業務部</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>其他</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>財務</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>會計</t>
+  </si>
+  <si>
+    <t>業務</t>
+  </si>
+  <si>
+    <t>MIS</t>
+  </si>
+  <si>
+    <t>人事</t>
+  </si>
+  <si>
+    <t>行政</t>
+  </si>
+  <si>
+    <t>環境</t>
+  </si>
+  <si>
+    <t>教育訓練</t>
   </si>
 </sst>
 </file>
@@ -575,111 +554,78 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="B4" s="2"/>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>6</v>
+      </c>
+      <c r="B5" s="2"/>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>7</v>
+      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>11</v>
+      </c>
+      <c r="B10" s="2"/>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="B11" s="2"/>
     </row>
     <row r="12" spans="1:2">
-      <c r="A12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B12" s="2"/>
     </row>
     <row r="13" spans="1:2">
-      <c r="A13" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A13" s="2"/>
+      <c r="B13" s="2"/>
     </row>
     <row r="14" spans="1:2">
-      <c r="A14" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="A14" s="2"/>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" s="2"/>
-      <c r="B15" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B15" s="2"/>
     </row>
     <row r="16" spans="1:2">
       <c r="A16" s="2"/>
-      <c r="B16" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="B16" s="2"/>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" s="2"/>

--- a/excel_files/其他科目.xlsx
+++ b/excel_files/其他科目.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\StephenData\excel_files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{931F8696-E18A-497D-8623-E8B40B37BEE1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A447FE3-AA57-468A-8876-80A46B5F1EA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{5854D81B-5B7B-4871-9FA3-56C4511C9373}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>工程案號</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -42,9 +42,6 @@
     <t>財務</t>
   </si>
   <si>
-    <t>-</t>
-  </si>
-  <si>
     <t>會計</t>
   </si>
   <si>
@@ -64,6 +61,42 @@
   </si>
   <si>
     <t>教育訓練</t>
+  </si>
+  <si>
+    <t>公司電腦或資料庫維護之類所屬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>其他未能成案之類所屬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司人事行政所屬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司一般行政所屬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>環境維護及修繕所屬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>公司內訓或外訓所屬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>尚未歸類所屬</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 會計事務</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve"> 財務類事務</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -537,7 +570,7 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="14.75" customWidth="1"/>
+    <col min="2" max="2" width="28.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -557,56 +590,72 @@
         <v>3</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2"/>
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="2"/>
+        <v>6</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="B9" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="2"/>
+        <v>10</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="2"/>
+      <c r="B11" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:2">
       <c r="B12" s="2"/>
